--- a/run/Info.xlsx
+++ b/run/Info.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20386"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF0213E-8544-4BA6-A22C-A895DE8D3B55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31B5CF5-7177-4372-898E-56278CE1A598}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>account</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -38,8 +38,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>index</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>claire881031</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ue487ad1b559280fffc466af017f47e79</t>
+  </si>
+  <si>
+    <t>Ub7e9f322724c6b15cab6fc57630e5d8c</t>
   </si>
 </sst>
 </file>
@@ -412,8 +422,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>410731220</v>
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>410731220</v>
@@ -432,14 +442,14 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>410831143</v>
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>410831143</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>23</v>

--- a/run/Info.xlsx
+++ b/run/Info.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20386"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31B5CF5-7177-4372-898E-56278CE1A598}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,20 +41,20 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>claire881031</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Ue487ad1b559280fffc466af017f47e79</t>
   </si>
   <si>
     <t>Ub7e9f322724c6b15cab6fc57630e5d8c</t>
+  </si>
+  <si>
+    <t>cla881031ire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -163,7 +162,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -198,7 +197,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -375,16 +374,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -423,7 +422,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>410731220</v>
@@ -443,13 +442,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>410831143</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>23</v>

--- a/run/Info.xlsx
+++ b/run/Info.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20386"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31B5CF5-7177-4372-898E-56278CE1A598}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,20 +42,20 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>claire881031</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Ue487ad1b559280fffc466af017f47e79</t>
   </si>
   <si>
     <t>Ub7e9f322724c6b15cab6fc57630e5d8c</t>
-  </si>
-  <si>
-    <t>cla881031ire</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -162,7 +163,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -197,7 +198,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -374,16 +375,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -422,7 +423,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>410731220</v>
@@ -442,13 +443,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>410831143</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>23</v>
